--- a/public/templates/planilla_proyectado.xlsx
+++ b/public/templates/planilla_proyectado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\tierrasanta\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24A7850-B78B-4B90-836F-1FDA76CAF283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1ACAEC-9E24-49BA-9A8A-EB5889556255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{0D0853FD-6A20-4A77-9B43-493267389889}"/>
   </bookViews>
